--- a/StructureDefinition-convergence-assessment.xlsx
+++ b/StructureDefinition-convergence-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-convergence-assessment.xlsx
+++ b/StructureDefinition-convergence-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1758,17 +1758,17 @@
   <dimension ref="A1:AP51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1777,28 +1777,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-convergence-assessment.xlsx
+++ b/StructureDefinition-convergence-assessment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="455">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Represents a qualitative assessment of convergence ability (good, fair,
+    <t>Represents a qualitative assessment of convergence ability (good, fair,
 insufficient, poor).</t>
   </si>
   <si>
@@ -630,6 +630,31 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:exam</t>
+  </si>
+  <si>
+    <t>exam</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -641,18 +666,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -670,6 +683,15 @@
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="convergence-assessment"/&gt;
+    &lt;display value="Convergence assessment"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>example</t>
@@ -1755,7 +1777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP51"/>
+  <dimension ref="A1:AP52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.10546875" customWidth="true" bestFit="true"/>
@@ -3491,7 +3513,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>191</v>
       </c>
@@ -3541,7 +3563,7 @@
         <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>83</v>
@@ -3559,25 +3581,23 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>191</v>
@@ -3604,10 +3624,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3615,14 +3635,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3638,22 +3660,22 @@
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3663,7 +3685,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3678,13 +3700,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3702,13 +3724,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3717,34 +3739,34 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3763,19 +3785,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -3785,7 +3807,7 @@
         <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>83</v>
@@ -3800,13 +3822,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -3824,10 +3846,10 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>94</v>
@@ -3839,30 +3861,30 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>83</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3870,13 +3892,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>83</v>
@@ -3885,18 +3907,20 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -3944,13 +3968,13 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
@@ -3959,19 +3983,19 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -3979,21 +4003,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4005,20 +4029,18 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4066,13 +4088,13 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
@@ -4081,19 +4103,19 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4101,14 +4123,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4127,19 +4149,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4188,7 +4210,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4203,19 +4225,19 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
@@ -4223,14 +4245,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4249,18 +4271,20 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4308,7 +4332,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4323,19 +4347,19 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4343,10 +4367,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4357,7 +4381,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4369,18 +4393,18 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4428,13 +4452,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4443,30 +4467,30 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4474,13 +4498,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>83</v>
@@ -4489,19 +4513,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4550,45 +4572,45 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>281</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4596,34 +4618,34 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4648,13 +4670,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4672,7 +4694,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4681,7 +4703,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -4690,38 +4712,38 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>137</v>
+        <v>284</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>293</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4736,16 +4758,16 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4770,40 +4792,40 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
@@ -4812,31 +4834,31 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>301</v>
+        <v>137</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>303</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4846,7 +4868,7 @@
         <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>83</v>
@@ -4855,19 +4877,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>305</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -4892,13 +4914,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -4916,7 +4938,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4934,27 +4956,27 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4965,10 +4987,10 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
@@ -4977,18 +4999,20 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>310</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5012,13 +5036,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>316</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5036,13 +5060,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5054,27 +5078,27 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5100,17 +5124,15 @@
         <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5134,13 +5156,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5158,7 +5180,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5176,27 +5198,27 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5219,18 +5241,20 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>332</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5254,13 +5278,13 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5278,7 +5302,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5296,27 +5320,27 @@
         <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>339</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5339,16 +5363,16 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5398,7 +5422,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5416,27 +5440,27 @@
         <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5447,7 +5471,7 @@
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -5459,20 +5483,18 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5520,45 +5542,45 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>355</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>83</v>
+        <v>350</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5569,7 +5591,7 @@
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5581,16 +5603,20 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5638,31 +5664,31 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5673,21 +5699,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5699,17 +5725,15 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>140</v>
+        <v>364</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -5758,19 +5782,19 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -5782,7 +5806,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -5793,14 +5817,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>368</v>
+        <v>139</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5813,16 +5837,16 @@
         <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>369</v>
+        <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
         <v>370</v>
@@ -5830,9 +5854,7 @@
       <c r="N34" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O34" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -5904,7 +5926,7 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>137</v>
+        <v>368</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -5922,26 +5944,26 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>373</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>373</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>374</v>
@@ -5949,8 +5971,12 @@
       <c r="M35" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="N35" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -5998,19 +6024,19 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>376</v>
+        <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6019,10 +6045,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>378</v>
+        <v>137</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6033,10 +6059,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6059,13 +6085,13 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6116,7 +6142,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6125,7 +6151,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6137,10 +6163,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6151,10 +6177,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6177,20 +6203,16 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>378</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N37" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="O37" t="s" s="2">
-        <v>387</v>
-      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6214,13 +6236,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6238,7 +6260,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6247,7 +6269,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6256,13 +6278,13 @@
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>302</v>
+        <v>387</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6273,10 +6295,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6287,7 +6309,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -6302,16 +6324,16 @@
         <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6336,13 +6358,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6360,13 +6382,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -6378,13 +6400,13 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6395,10 +6417,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6409,7 +6431,7 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>83</v>
@@ -6421,17 +6443,19 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6456,13 +6480,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6480,13 +6504,13 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
@@ -6498,13 +6522,13 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>83</v>
+        <v>395</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>404</v>
+        <v>307</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6515,10 +6539,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6541,7 +6565,7 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>359</v>
+        <v>405</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>406</v>
@@ -6550,7 +6574,9 @@
         <v>407</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6598,7 +6624,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6619,10 +6645,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6633,10 +6659,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6647,7 +6673,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6656,10 +6682,10 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>410</v>
+        <v>364</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>411</v>
@@ -6667,9 +6693,7 @@
       <c r="M41" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N41" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6718,13 +6742,13 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
@@ -6739,10 +6763,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6753,10 +6777,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6779,16 +6803,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6838,7 +6862,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6859,10 +6883,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -6873,10 +6897,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6899,7 +6923,7 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>350</v>
+        <v>422</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>423</v>
@@ -6910,9 +6934,7 @@
       <c r="N43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>426</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -6960,7 +6982,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6981,10 +7003,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -6995,10 +7017,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7009,7 +7031,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7018,19 +7040,23 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>360</v>
+        <v>428</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7078,19 +7104,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>427</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7099,10 +7125,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>432</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>363</v>
+        <v>433</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7113,21 +7139,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -7139,17 +7165,15 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>140</v>
+        <v>364</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7198,19 +7222,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7222,7 +7246,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7233,14 +7257,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>368</v>
+        <v>139</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7253,16 +7277,16 @@
         <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>369</v>
+        <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>370</v>
@@ -7270,9 +7294,7 @@
       <c r="N46" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7344,7 +7366,7 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>137</v>
+        <v>368</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7355,45 +7377,45 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>435</v>
+        <v>143</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7418,13 +7440,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7442,34 +7464,34 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>432</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>436</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7488,7 +7510,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>94</v>
@@ -7503,19 +7525,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>440</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7540,13 +7562,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7567,7 +7589,7 @@
         <v>437</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>94</v>
@@ -7585,16 +7607,16 @@
         <v>441</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>280</v>
+        <v>219</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>281</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -7622,22 +7644,22 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>443</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>444</v>
+        <v>279</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>445</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7662,13 +7684,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7695,7 +7717,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7704,38 +7726,38 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>137</v>
+        <v>284</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>83</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>293</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7750,16 +7772,16 @@
         <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>294</v>
+        <v>448</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>295</v>
+        <v>449</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>296</v>
+        <v>450</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7784,13 +7806,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7808,16 +7830,16 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -7826,31 +7848,31 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>301</v>
+        <v>137</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>303</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7869,19 +7891,19 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>448</v>
+        <v>299</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>449</v>
+        <v>300</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>353</v>
+        <v>301</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -7906,13 +7928,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -7930,7 +7952,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7948,23 +7970,145 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>356</v>
+        <v>306</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP51">
+  <autoFilter ref="A1:AP52">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7974,7 +8118,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI50">
+  <conditionalFormatting sqref="A2:AI51">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
